--- a/Deliverables/BOM/BOB_MCF8316/eSpark_BOM_BOB.xlsx
+++ b/Deliverables/BOM/BOB_MCF8316/eSpark_BOM_BOB.xlsx
@@ -5,12 +5,12 @@
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HP\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub\Mahmood-PTZKeyboard\Deliverables\BOM\BOB_MCF8316\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D97A8166-CEBD-4A4F-9B25-EAB2C2521F06}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3D72DF51-5E22-404C-AF6A-09FDA2330FAB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1950" yWindow="840" windowWidth="11790" windowHeight="15360" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="306" uniqueCount="203">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="309" uniqueCount="206">
   <si>
     <t>Component list</t>
   </si>
@@ -539,9 +539,6 @@
     <t>C8483</t>
   </si>
   <si>
-    <t>C358687</t>
-  </si>
-  <si>
     <t>C132810</t>
   </si>
   <si>
@@ -626,9 +623,6 @@
     <t>RC0603FR-0722RL</t>
   </si>
   <si>
-    <t>MTP125-1105S1</t>
-  </si>
-  <si>
     <t>RC0402FR-071KL</t>
   </si>
   <si>
@@ -639,6 +633,21 @@
   </si>
   <si>
     <t>Custom Supplier</t>
+  </si>
+  <si>
+    <t>MTP125-1106S1</t>
+  </si>
+  <si>
+    <t>C358688</t>
+  </si>
+  <si>
+    <t>YAGEO</t>
+  </si>
+  <si>
+    <t>TDK Corporation</t>
+  </si>
+  <si>
+    <t>FH</t>
   </si>
 </sst>
 </file>
@@ -1750,7 +1759,7 @@
       </c>
       <c r="E2" s="11"/>
       <c r="F2" s="55" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="G2" s="12"/>
       <c r="H2" s="4"/>
@@ -1775,7 +1784,7 @@
       </c>
       <c r="E3" s="13"/>
       <c r="F3" s="56" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="G3" s="13"/>
       <c r="H3" s="5"/>
@@ -1800,7 +1809,7 @@
       </c>
       <c r="E4" s="13"/>
       <c r="F4" s="57" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="G4" s="14"/>
       <c r="H4" s="7"/>
@@ -1940,19 +1949,19 @@
         <v>135</v>
       </c>
       <c r="M9" s="30" t="s">
+        <v>190</v>
+      </c>
+      <c r="N9" s="30" t="s">
         <v>191</v>
-      </c>
-      <c r="N9" s="30" t="s">
-        <v>192</v>
       </c>
       <c r="O9" s="30" t="s">
         <v>140</v>
       </c>
       <c r="P9" s="30" t="s">
+        <v>192</v>
+      </c>
+      <c r="Q9" s="30" t="s">
         <v>193</v>
-      </c>
-      <c r="Q9" s="30" t="s">
-        <v>194</v>
       </c>
       <c r="R9" s="32" t="s">
         <v>141</v>
@@ -1986,7 +1995,7 @@
         <v>100</v>
       </c>
       <c r="I10" s="46" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="J10" s="46" t="s">
         <v>153</v>
@@ -2005,7 +2014,7 @@
         <v>20</v>
       </c>
       <c r="O10" s="61" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="P10" s="53">
         <v>3.32E-2</v>
@@ -2033,16 +2042,16 @@
         <v>37</v>
       </c>
       <c r="F11" s="50" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="G11" s="51" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="H11" s="50" t="s">
         <v>101</v>
       </c>
       <c r="I11" s="50" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="J11" s="50" t="s">
         <v>154</v>
@@ -2061,7 +2070,7 @@
         <v>12</v>
       </c>
       <c r="O11" s="62" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="P11" s="54">
         <v>0.37869999999999998</v>
@@ -2098,7 +2107,7 @@
         <v>102</v>
       </c>
       <c r="I12" s="46" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="J12" s="46" t="s">
         <v>155</v>
@@ -2117,7 +2126,7 @@
         <v>25</v>
       </c>
       <c r="O12" s="61" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="P12" s="53">
         <v>0.13780000000000001</v>
@@ -2154,7 +2163,7 @@
         <v>100</v>
       </c>
       <c r="I13" s="50" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="J13" s="50" t="s">
         <v>156</v>
@@ -2173,7 +2182,7 @@
         <v>100</v>
       </c>
       <c r="O13" s="62" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="P13" s="54">
         <v>5.3E-3</v>
@@ -2204,11 +2213,13 @@
         <v>65</v>
       </c>
       <c r="G14" s="47" t="s">
-        <v>183</v>
-      </c>
-      <c r="H14" s="46"/>
+        <v>182</v>
+      </c>
+      <c r="H14" s="46" t="s">
+        <v>203</v>
+      </c>
       <c r="I14" s="46" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="J14" s="46" t="s">
         <v>157</v>
@@ -2227,7 +2238,7 @@
         <v>50</v>
       </c>
       <c r="O14" s="61" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="P14" s="53">
         <v>8.3999999999999995E-3</v>
@@ -2264,7 +2275,7 @@
         <v>100</v>
       </c>
       <c r="I15" s="50" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="J15" s="50" t="s">
         <v>158</v>
@@ -2283,7 +2294,7 @@
         <v>100</v>
       </c>
       <c r="O15" s="62" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="P15" s="54">
         <v>6.0000000000000001E-3</v>
@@ -2320,7 +2331,7 @@
         <v>100</v>
       </c>
       <c r="I16" s="46" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="J16" s="46" t="s">
         <v>159</v>
@@ -2339,7 +2350,7 @@
         <v>50</v>
       </c>
       <c r="O16" s="61" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="P16" s="53">
         <v>1.3100000000000001E-2</v>
@@ -2376,7 +2387,7 @@
         <v>103</v>
       </c>
       <c r="I17" s="50" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="J17" s="50" t="s">
         <v>160</v>
@@ -2395,7 +2406,7 @@
         <v>12</v>
       </c>
       <c r="O17" s="62" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="P17" s="54">
         <v>0.8125</v>
@@ -2432,7 +2443,7 @@
         <v>104</v>
       </c>
       <c r="I18" s="46" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="J18" s="46" t="s">
         <v>161</v>
@@ -2451,7 +2462,7 @@
         <v>100</v>
       </c>
       <c r="O18" s="61" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="P18" s="53">
         <v>4.5999999999999999E-3</v>
@@ -2488,13 +2499,13 @@
         <v>105</v>
       </c>
       <c r="I19" s="50" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="J19" s="50" t="s">
         <v>162</v>
       </c>
       <c r="K19" s="50" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="L19" s="51">
         <v>1</v>
@@ -2507,7 +2518,7 @@
         <v>20</v>
       </c>
       <c r="O19" s="62" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="P19" s="54">
         <v>4.3099999999999999E-2</v>
@@ -2538,11 +2549,13 @@
         <v>70</v>
       </c>
       <c r="G20" s="47" t="s">
-        <v>184</v>
-      </c>
-      <c r="H20" s="46"/>
+        <v>183</v>
+      </c>
+      <c r="H20" s="46" t="s">
+        <v>204</v>
+      </c>
       <c r="I20" s="46" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="J20" s="46" t="s">
         <v>163</v>
@@ -2561,7 +2574,7 @@
         <v>15</v>
       </c>
       <c r="O20" s="61" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="P20" s="53">
         <v>0.18379999999999999</v>
@@ -2592,11 +2605,13 @@
         <v>70</v>
       </c>
       <c r="G21" s="51" t="s">
-        <v>185</v>
-      </c>
-      <c r="H21" s="50"/>
+        <v>184</v>
+      </c>
+      <c r="H21" s="50" t="s">
+        <v>205</v>
+      </c>
       <c r="I21" s="50" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="J21" s="50" t="s">
         <v>164</v>
@@ -2615,7 +2630,7 @@
         <v>50</v>
       </c>
       <c r="O21" s="62" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="P21" s="54">
         <v>1.5599999999999999E-2</v>
@@ -2650,7 +2665,7 @@
         <v>106</v>
       </c>
       <c r="I22" s="46" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="J22" s="46" t="s">
         <v>165</v>
@@ -2669,7 +2684,7 @@
         <v>15</v>
       </c>
       <c r="O22" s="61" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="P22" s="53">
         <v>9.7900000000000001E-2</v>
@@ -2706,7 +2721,7 @@
         <v>107</v>
       </c>
       <c r="I23" s="50" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="J23" s="50" t="s">
         <v>166</v>
@@ -2725,7 +2740,7 @@
         <v>20</v>
       </c>
       <c r="O23" s="62" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="P23" s="54">
         <v>4.2099999999999999E-2</v>
@@ -2762,7 +2777,7 @@
         <v>108</v>
       </c>
       <c r="I24" s="46" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="J24" s="46" t="s">
         <v>167</v>
@@ -2781,7 +2796,7 @@
         <v>20</v>
       </c>
       <c r="O24" s="61" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="P24" s="53">
         <v>6.93E-2</v>
@@ -2809,7 +2824,7 @@
         <v>51</v>
       </c>
       <c r="F25" s="50" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="G25" s="51" t="s">
         <v>73</v>
@@ -2818,13 +2833,13 @@
         <v>109</v>
       </c>
       <c r="I25" s="50" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="J25" s="50" t="s">
         <v>168</v>
       </c>
       <c r="K25" s="50" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="L25" s="51">
         <v>2</v>
@@ -2837,7 +2852,7 @@
         <v>25</v>
       </c>
       <c r="O25" s="62" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="P25" s="54">
         <v>0.1351</v>
@@ -2874,13 +2889,13 @@
         <v>104</v>
       </c>
       <c r="I26" s="46" t="s">
-        <v>198</v>
+        <v>201</v>
       </c>
       <c r="J26" s="46" t="s">
-        <v>169</v>
+        <v>202</v>
       </c>
       <c r="K26" s="46" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="L26" s="47">
         <v>2</v>
@@ -2893,14 +2908,14 @@
         <v>40</v>
       </c>
       <c r="O26" s="61" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="P26" s="53">
-        <v>3.1399999999999997E-2</v>
+        <v>2.6800000000000001E-2</v>
       </c>
       <c r="Q26" s="53">
         <f t="shared" si="2"/>
-        <v>1.2559999999999998</v>
+        <v>1.0720000000000001</v>
       </c>
       <c r="R26" s="48"/>
       <c r="S26" s="48"/>
@@ -2927,16 +2942,16 @@
         <v>128</v>
       </c>
       <c r="H27" s="50" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="I27" s="50" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="J27" s="50" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="K27" s="50" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="L27" s="51">
         <v>1</v>
@@ -2949,7 +2964,7 @@
         <v>20</v>
       </c>
       <c r="O27" s="62" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="P27" s="54">
         <v>2.1899999999999999E-2</v>
@@ -2983,16 +2998,16 @@
         <v>129</v>
       </c>
       <c r="H28" s="46" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="I28" s="46" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="J28" s="46" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="K28" s="46" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="L28" s="47">
         <v>1</v>
@@ -3005,7 +3020,7 @@
         <v>15</v>
       </c>
       <c r="O28" s="61" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="P28" s="53">
         <v>0.20269999999999999</v>
@@ -3036,16 +3051,16 @@
         <v>77</v>
       </c>
       <c r="G29" s="65" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="H29" s="50" t="s">
         <v>110</v>
       </c>
       <c r="I29" s="50" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="J29" s="50" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="K29" s="50" t="s">
         <v>130</v>
@@ -3061,7 +3076,7 @@
         <v>100</v>
       </c>
       <c r="O29" s="62" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="P29" s="54">
         <v>1.4E-3</v>
@@ -3098,10 +3113,10 @@
         <v>100</v>
       </c>
       <c r="I30" s="46" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="J30" s="46" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="K30" s="46" t="s">
         <v>131</v>
@@ -3117,7 +3132,7 @@
         <v>100</v>
       </c>
       <c r="O30" s="61" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="P30" s="53">
         <v>1.6999999999999999E-3</v>
@@ -3154,10 +3169,10 @@
         <v>111</v>
       </c>
       <c r="I31" s="50" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="J31" s="50" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="K31" s="50" t="s">
         <v>132</v>
@@ -3173,7 +3188,7 @@
         <v>100</v>
       </c>
       <c r="O31" s="62" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="P31" s="54">
         <v>6.9999999999999999E-4</v>
@@ -3210,10 +3225,10 @@
         <v>100</v>
       </c>
       <c r="I32" s="46" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="J32" s="46" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="K32" s="46" t="s">
         <v>133</v>
@@ -3229,7 +3244,7 @@
         <v>100</v>
       </c>
       <c r="O32" s="61" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="P32" s="53">
         <v>1E-3</v>
@@ -3266,10 +3281,10 @@
         <v>100</v>
       </c>
       <c r="I33" s="50" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="J33" s="50" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="K33" s="50" t="s">
         <v>134</v>
@@ -3285,7 +3300,7 @@
         <v>100</v>
       </c>
       <c r="O33" s="62" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="P33" s="54">
         <v>1.1999999999999999E-3</v>
@@ -3313,22 +3328,22 @@
         <v>60</v>
       </c>
       <c r="F34" s="46" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="G34" s="47" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="H34" s="46" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="I34" s="46" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="J34" s="46" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="K34" s="46" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="L34" s="47">
         <v>5</v>
@@ -3338,22 +3353,22 @@
         <v>50</v>
       </c>
       <c r="N34" s="46" t="s">
+        <v>187</v>
+      </c>
+      <c r="O34" s="46" t="s">
+        <v>187</v>
+      </c>
+      <c r="P34" s="53" t="s">
+        <v>187</v>
+      </c>
+      <c r="Q34" s="53" t="s">
+        <v>187</v>
+      </c>
+      <c r="R34" s="64" t="s">
         <v>188</v>
       </c>
-      <c r="O34" s="46" t="s">
-        <v>188</v>
-      </c>
-      <c r="P34" s="53" t="s">
-        <v>188</v>
-      </c>
-      <c r="Q34" s="53" t="s">
-        <v>188</v>
-      </c>
-      <c r="R34" s="64" t="s">
-        <v>189</v>
-      </c>
       <c r="S34" s="53" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
     </row>
     <row r="35" spans="1:19" ht="48.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -3372,7 +3387,7 @@
         <v>61</v>
       </c>
       <c r="F35" s="50" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="G35" s="51" t="s">
         <v>96</v>
@@ -3381,13 +3396,13 @@
         <v>112</v>
       </c>
       <c r="I35" s="50" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="J35" s="50" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="K35" s="50" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="L35" s="51">
         <v>3</v>
@@ -3400,7 +3415,7 @@
         <v>33</v>
       </c>
       <c r="O35" s="62" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="P35" s="54">
         <v>0.2752</v>
@@ -3437,13 +3452,13 @@
         <v>113</v>
       </c>
       <c r="I36" s="46" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="J36" s="46" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="K36" s="46" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="L36" s="47">
         <v>1</v>
@@ -3456,7 +3471,7 @@
         <v>11</v>
       </c>
       <c r="O36" s="61" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="P36" s="53">
         <v>2.4839000000000002</v>
@@ -3493,11 +3508,11 @@
         <v>114</v>
       </c>
       <c r="I37" s="50" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="J37" s="50"/>
       <c r="K37" s="50" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="L37" s="51">
         <v>1</v>
@@ -3510,7 +3525,7 @@
         <v>11</v>
       </c>
       <c r="O37" s="62" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="P37" s="54">
         <v>5.15</v>
@@ -3537,13 +3552,13 @@
       <c r="L38" s="37"/>
       <c r="M38" s="37"/>
       <c r="N38" s="77" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="O38" s="78"/>
       <c r="P38" s="78"/>
       <c r="Q38" s="67">
         <f>SUM(Q10:Q37)</f>
-        <v>130.93040000000002</v>
+        <v>130.74640000000002</v>
       </c>
       <c r="R38" s="73"/>
       <c r="S38" s="74"/>
@@ -3563,13 +3578,13 @@
       <c r="L39" s="10"/>
       <c r="M39" s="10"/>
       <c r="N39" s="77" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="O39" s="78"/>
       <c r="P39" s="78"/>
       <c r="Q39" s="68">
         <f>Q38/10</f>
-        <v>13.093040000000002</v>
+        <v>13.074640000000002</v>
       </c>
       <c r="R39" s="75"/>
       <c r="S39" s="76"/>
@@ -3606,9 +3621,9 @@
     <hyperlink ref="O36" r:id="rId21" xr:uid="{01E3417C-EB7C-49EE-A0C1-F26D70C08CA9}"/>
     <hyperlink ref="O35" r:id="rId22" xr:uid="{170A10E6-2632-4E80-9290-22C344C8B67F}"/>
     <hyperlink ref="O18" r:id="rId23" xr:uid="{ACA5EFEC-F85C-48B9-8C67-8CE59A6B862F}"/>
-    <hyperlink ref="O26" r:id="rId24" xr:uid="{19D7451A-5A3A-4A47-999C-A6B3C9F51E8F}"/>
-    <hyperlink ref="O29" r:id="rId25" xr:uid="{091CBD23-D921-4015-985B-E6E20A2DF817}"/>
-    <hyperlink ref="O31" r:id="rId26" xr:uid="{8575D59F-B099-440F-800D-AFD59FD7E1E8}"/>
+    <hyperlink ref="O29" r:id="rId24" xr:uid="{091CBD23-D921-4015-985B-E6E20A2DF817}"/>
+    <hyperlink ref="O31" r:id="rId25" xr:uid="{8575D59F-B099-440F-800D-AFD59FD7E1E8}"/>
+    <hyperlink ref="O26" r:id="rId26" xr:uid="{676A6DD4-A39A-4B44-91A9-93161623CA1F}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId27"/>

--- a/Deliverables/BOM/BOB_MCF8316/eSpark_BOM_BOB.xlsx
+++ b/Deliverables/BOM/BOB_MCF8316/eSpark_BOM_BOB.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="25629"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="25726"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub\Mahmood-PTZKeyboard\Deliverables\BOM\BOB_MCF8316\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3D72DF51-5E22-404C-AF6A-09FDA2330FAB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{080DB6A0-A886-4C5B-A2A6-1D647406E8E5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="309" uniqueCount="206">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="319" uniqueCount="215">
   <si>
     <t>Component list</t>
   </si>
@@ -68,9 +68,6 @@
     <t>C7, C8</t>
   </si>
   <si>
-    <t>C9, C10, C12</t>
-  </si>
-  <si>
     <t>C11</t>
   </si>
   <si>
@@ -98,12 +95,6 @@
     <t>LED2</t>
   </si>
   <si>
-    <t>P1, P2</t>
-  </si>
-  <si>
-    <t>P3, P4</t>
-  </si>
-  <si>
     <t>Q1</t>
   </si>
   <si>
@@ -119,12 +110,6 @@
     <t>R6</t>
   </si>
   <si>
-    <t>R7</t>
-  </si>
-  <si>
-    <t>R13, R14, R18, R19</t>
-  </si>
-  <si>
     <t>SB1, SB2, SB3, SB4, SB5</t>
   </si>
   <si>
@@ -158,9 +143,6 @@
     <t>CAP CER 1UF 25V X5R 0603</t>
   </si>
   <si>
-    <t>CAP CER 47PF 100V NPO 0603</t>
-  </si>
-  <si>
     <t>CAP TANT 100UF 20% 25V 2917</t>
   </si>
   <si>
@@ -206,9 +188,6 @@
     <t>RES SMD 1K OHM 5% 1/10W 0402</t>
   </si>
   <si>
-    <t>RES SMD 4.7K OHM 5% 1/10W 0603</t>
-  </si>
-  <si>
     <t>RES SMD 5.1K OHM 5% 1/10W 0603</t>
   </si>
   <si>
@@ -290,9 +269,6 @@
     <t>CC0603KRX5R8BB105</t>
   </si>
   <si>
-    <t>AC0603JRNPO0BN470</t>
-  </si>
-  <si>
     <t>TAJE107M025RNJ</t>
   </si>
   <si>
@@ -314,9 +290,6 @@
     <t>ERJ-2GEJ102X</t>
   </si>
   <si>
-    <t>RC0603JR-074K7L</t>
-  </si>
-  <si>
     <t>RC0603JR-075K1L</t>
   </si>
   <si>
@@ -392,9 +365,6 @@
     <t>10nF</t>
   </si>
   <si>
-    <t>47pF</t>
-  </si>
-  <si>
     <t>100uF</t>
   </si>
   <si>
@@ -509,9 +479,6 @@
     <t>C14664</t>
   </si>
   <si>
-    <t>C389107</t>
-  </si>
-  <si>
     <t>C7230</t>
   </si>
   <si>
@@ -554,9 +521,6 @@
     <t>C2935237</t>
   </si>
   <si>
-    <t>C105428</t>
-  </si>
-  <si>
     <t>C14677</t>
   </si>
   <si>
@@ -648,6 +612,69 @@
   </si>
   <si>
     <t>FH</t>
+  </si>
+  <si>
+    <t>C9, C10</t>
+  </si>
+  <si>
+    <t>CAP CER 0.047UF 50V X8R 0603</t>
+  </si>
+  <si>
+    <t>CGA3E2X8R1H473M080AA</t>
+  </si>
+  <si>
+    <t>TDK</t>
+  </si>
+  <si>
+    <t>CGA3E2X8R1H473KT0Y0H</t>
+  </si>
+  <si>
+    <t>47nF</t>
+  </si>
+  <si>
+    <t>C12</t>
+  </si>
+  <si>
+    <t>CAP CER 1UF 50V X7R 0603</t>
+  </si>
+  <si>
+    <t>UMK107AB7105KA-T</t>
+  </si>
+  <si>
+    <t>Taiyo Yuden</t>
+  </si>
+  <si>
+    <t>C342975</t>
+  </si>
+  <si>
+    <t>C105174</t>
+  </si>
+  <si>
+    <t>R7, R12, R13, R14, R15, R18, R19</t>
+  </si>
+  <si>
+    <t>R16</t>
+  </si>
+  <si>
+    <t>Res Thick Film 0805 4.7K Ohm 1% 0.5W ±100ppm/°C Molded SMD SMD Paper T/R</t>
+  </si>
+  <si>
+    <t>RES-0805</t>
+  </si>
+  <si>
+    <t>CRCW08054K70FKEAHP</t>
+  </si>
+  <si>
+    <t>Vishay</t>
+  </si>
+  <si>
+    <t>C313926</t>
+  </si>
+  <si>
+    <t>P1, P4</t>
+  </si>
+  <si>
+    <t>P2, P3</t>
   </si>
 </sst>
 </file>
@@ -868,7 +895,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="24">
+  <borders count="23">
     <border>
       <left/>
       <right/>
@@ -1102,21 +1129,6 @@
       <left style="medium">
         <color indexed="64"/>
       </left>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color indexed="64"/>
-      </left>
       <right/>
       <top style="medium">
         <color indexed="64"/>
@@ -1144,7 +1156,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="79">
+  <cellXfs count="78">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -1314,12 +1326,6 @@
     <xf numFmtId="0" fontId="21" fillId="4" borderId="17" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="4" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="22" fillId="2" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="23" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1329,7 +1335,7 @@
     <xf numFmtId="166" fontId="15" fillId="3" borderId="15" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="166" fontId="15" fillId="3" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="15" fillId="3" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1356,13 +1362,16 @@
     <xf numFmtId="0" fontId="17" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="3" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="24" fillId="3" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="top"/>
       <protection locked="0"/>
     </xf>
     <xf numFmtId="0" fontId="24" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="top"/>
       <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="4" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -1706,7 +1715,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:S39"/>
+  <dimension ref="A1:S40"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="3.140625" style="26" customWidth="1"/>
@@ -1740,15 +1749,15 @@
       <c r="H1" s="2"/>
       <c r="I1" s="2"/>
       <c r="J1" s="2"/>
-      <c r="K1" s="69"/>
-      <c r="L1" s="69"/>
-      <c r="M1" s="69"/>
-      <c r="N1" s="69"/>
-      <c r="O1" s="69"/>
-      <c r="P1" s="69"/>
-      <c r="Q1" s="69"/>
-      <c r="R1" s="69"/>
-      <c r="S1" s="70"/>
+      <c r="K1" s="67"/>
+      <c r="L1" s="67"/>
+      <c r="M1" s="67"/>
+      <c r="N1" s="67"/>
+      <c r="O1" s="67"/>
+      <c r="P1" s="67"/>
+      <c r="Q1" s="67"/>
+      <c r="R1" s="67"/>
+      <c r="S1" s="68"/>
     </row>
     <row r="2" spans="1:19" ht="32.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="1"/>
@@ -1759,7 +1768,7 @@
       </c>
       <c r="E2" s="11"/>
       <c r="F2" s="55" t="s">
-        <v>179</v>
+        <v>167</v>
       </c>
       <c r="G2" s="12"/>
       <c r="H2" s="4"/>
@@ -1784,7 +1793,7 @@
       </c>
       <c r="E3" s="13"/>
       <c r="F3" s="56" t="s">
-        <v>180</v>
+        <v>168</v>
       </c>
       <c r="G3" s="13"/>
       <c r="H3" s="5"/>
@@ -1798,7 +1807,7 @@
       <c r="P3" s="5"/>
       <c r="Q3" s="5"/>
       <c r="R3" s="5"/>
-      <c r="S3" s="71"/>
+      <c r="S3" s="69"/>
     </row>
     <row r="4" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A4" s="1"/>
@@ -1809,7 +1818,7 @@
       </c>
       <c r="E4" s="13"/>
       <c r="F4" s="57" t="s">
-        <v>180</v>
+        <v>168</v>
       </c>
       <c r="G4" s="14"/>
       <c r="H4" s="7"/>
@@ -1823,7 +1832,7 @@
       <c r="P4" s="6"/>
       <c r="Q4" s="6"/>
       <c r="R4" s="6"/>
-      <c r="S4" s="72"/>
+      <c r="S4" s="70"/>
     </row>
     <row r="5" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A5" s="1"/>
@@ -1848,7 +1857,7 @@
       <c r="P5" s="6"/>
       <c r="Q5" s="6"/>
       <c r="R5" s="6"/>
-      <c r="S5" s="72"/>
+      <c r="S5" s="70"/>
     </row>
     <row r="6" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A6" s="1"/>
@@ -1869,7 +1878,7 @@
       <c r="P6" s="6"/>
       <c r="Q6" s="6"/>
       <c r="R6" s="6"/>
-      <c r="S6" s="72"/>
+      <c r="S6" s="70"/>
     </row>
     <row r="7" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A7" s="1"/>
@@ -1890,7 +1899,7 @@
       <c r="P7" s="8"/>
       <c r="Q7" s="8"/>
       <c r="R7" s="8"/>
-      <c r="S7" s="72"/>
+      <c r="S7" s="70"/>
     </row>
     <row r="8" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A8" s="1"/>
@@ -1911,7 +1920,7 @@
       <c r="P8" s="8"/>
       <c r="Q8" s="8"/>
       <c r="R8" s="8"/>
-      <c r="S8" s="72"/>
+      <c r="S8" s="70"/>
     </row>
     <row r="9" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A9" s="1"/>
@@ -1919,55 +1928,55 @@
         <v>4</v>
       </c>
       <c r="C9" s="30" t="s">
-        <v>136</v>
+        <v>126</v>
       </c>
       <c r="D9" s="30" t="s">
         <v>6</v>
       </c>
       <c r="E9" s="31" t="s">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="F9" s="30" t="s">
-        <v>64</v>
+        <v>57</v>
       </c>
       <c r="G9" s="31" t="s">
-        <v>81</v>
+        <v>74</v>
       </c>
       <c r="H9" s="30" t="s">
-        <v>99</v>
+        <v>90</v>
       </c>
       <c r="I9" s="30" t="s">
-        <v>137</v>
+        <v>127</v>
       </c>
       <c r="J9" s="30" t="s">
-        <v>138</v>
+        <v>128</v>
       </c>
       <c r="K9" s="30" t="s">
-        <v>139</v>
+        <v>129</v>
       </c>
       <c r="L9" s="31" t="s">
-        <v>135</v>
+        <v>125</v>
       </c>
       <c r="M9" s="30" t="s">
-        <v>190</v>
+        <v>178</v>
       </c>
       <c r="N9" s="30" t="s">
-        <v>191</v>
+        <v>179</v>
       </c>
       <c r="O9" s="30" t="s">
-        <v>140</v>
+        <v>130</v>
       </c>
       <c r="P9" s="30" t="s">
-        <v>192</v>
+        <v>180</v>
       </c>
       <c r="Q9" s="30" t="s">
-        <v>193</v>
+        <v>181</v>
       </c>
       <c r="R9" s="32" t="s">
-        <v>141</v>
+        <v>131</v>
       </c>
       <c r="S9" s="32" t="s">
-        <v>142</v>
+        <v>132</v>
       </c>
     </row>
     <row r="10" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -1977,31 +1986,31 @@
         <v>1</v>
       </c>
       <c r="C10" s="59" t="s">
-        <v>143</v>
+        <v>133</v>
       </c>
       <c r="D10" s="46" t="s">
         <v>7</v>
       </c>
       <c r="E10" s="47" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="F10" s="46" t="s">
-        <v>65</v>
+        <v>58</v>
       </c>
       <c r="G10" s="47" t="s">
-        <v>82</v>
+        <v>75</v>
       </c>
       <c r="H10" s="46" t="s">
-        <v>100</v>
+        <v>91</v>
       </c>
       <c r="I10" s="46" t="s">
-        <v>187</v>
+        <v>175</v>
       </c>
       <c r="J10" s="46" t="s">
-        <v>153</v>
+        <v>143</v>
       </c>
       <c r="K10" s="46" t="s">
-        <v>115</v>
+        <v>106</v>
       </c>
       <c r="L10" s="47">
         <v>1</v>
@@ -2014,7 +2023,7 @@
         <v>20</v>
       </c>
       <c r="O10" s="61" t="s">
-        <v>178</v>
+        <v>166</v>
       </c>
       <c r="P10" s="53">
         <v>3.32E-2</v>
@@ -2029,54 +2038,54 @@
     <row r="11" spans="1:19" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A11" s="1"/>
       <c r="B11" s="38">
-        <f t="shared" ref="B11:B37" si="0">ROW(B11) - ROW($B$9)</f>
+        <f t="shared" ref="B11:B38" si="0">ROW(B11) - ROW($B$9)</f>
         <v>2</v>
       </c>
       <c r="C11" s="60" t="s">
-        <v>143</v>
+        <v>133</v>
       </c>
       <c r="D11" s="50" t="s">
         <v>8</v>
       </c>
       <c r="E11" s="51" t="s">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="F11" s="50" t="s">
-        <v>189</v>
+        <v>177</v>
       </c>
       <c r="G11" s="51" t="s">
-        <v>181</v>
+        <v>169</v>
       </c>
       <c r="H11" s="50" t="s">
-        <v>101</v>
+        <v>92</v>
       </c>
       <c r="I11" s="50" t="s">
-        <v>187</v>
+        <v>175</v>
       </c>
       <c r="J11" s="50" t="s">
-        <v>154</v>
+        <v>144</v>
       </c>
       <c r="K11" s="50" t="s">
-        <v>116</v>
+        <v>107</v>
       </c>
       <c r="L11" s="51">
         <v>1</v>
       </c>
       <c r="M11" s="50">
-        <f t="shared" ref="M11:M37" si="1">L11*10</f>
+        <f t="shared" ref="M11:M38" si="1">L11*10</f>
         <v>10</v>
       </c>
       <c r="N11" s="50">
         <v>12</v>
       </c>
       <c r="O11" s="62" t="s">
-        <v>178</v>
+        <v>166</v>
       </c>
       <c r="P11" s="54">
         <v>0.37869999999999998</v>
       </c>
       <c r="Q11" s="54">
-        <f t="shared" ref="Q11:Q37" si="2">P11*N11</f>
+        <f t="shared" ref="Q11:Q38" si="2">P11*N11</f>
         <v>4.5443999999999996</v>
       </c>
       <c r="R11" s="52"/>
@@ -2085,35 +2094,35 @@
     <row r="12" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A12" s="1"/>
       <c r="B12" s="38">
-        <f>ROW(B12) - ROW($B$9)</f>
+        <f t="shared" si="0"/>
         <v>3</v>
       </c>
       <c r="C12" s="59" t="s">
-        <v>143</v>
+        <v>133</v>
       </c>
       <c r="D12" s="46" t="s">
         <v>9</v>
       </c>
       <c r="E12" s="47" t="s">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="F12" s="46" t="s">
-        <v>66</v>
+        <v>59</v>
       </c>
       <c r="G12" s="47" t="s">
-        <v>83</v>
+        <v>76</v>
       </c>
       <c r="H12" s="46" t="s">
-        <v>102</v>
+        <v>93</v>
       </c>
       <c r="I12" s="46" t="s">
-        <v>187</v>
+        <v>175</v>
       </c>
       <c r="J12" s="46" t="s">
-        <v>155</v>
+        <v>145</v>
       </c>
       <c r="K12" s="46" t="s">
-        <v>117</v>
+        <v>108</v>
       </c>
       <c r="L12" s="47">
         <v>2</v>
@@ -2126,7 +2135,7 @@
         <v>25</v>
       </c>
       <c r="O12" s="61" t="s">
-        <v>178</v>
+        <v>166</v>
       </c>
       <c r="P12" s="53">
         <v>0.13780000000000001</v>
@@ -2145,31 +2154,31 @@
         <v>4</v>
       </c>
       <c r="C13" s="60" t="s">
-        <v>143</v>
+        <v>133</v>
       </c>
       <c r="D13" s="50" t="s">
         <v>10</v>
       </c>
       <c r="E13" s="51" t="s">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="F13" s="50" t="s">
-        <v>65</v>
+        <v>58</v>
       </c>
       <c r="G13" s="51" t="s">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="H13" s="50" t="s">
-        <v>100</v>
+        <v>91</v>
       </c>
       <c r="I13" s="50" t="s">
-        <v>187</v>
+        <v>175</v>
       </c>
       <c r="J13" s="50" t="s">
-        <v>156</v>
+        <v>146</v>
       </c>
       <c r="K13" s="50" t="s">
-        <v>118</v>
+        <v>109</v>
       </c>
       <c r="L13" s="51">
         <v>4</v>
@@ -2182,7 +2191,7 @@
         <v>100</v>
       </c>
       <c r="O13" s="62" t="s">
-        <v>178</v>
+        <v>166</v>
       </c>
       <c r="P13" s="54">
         <v>5.3E-3</v>
@@ -2197,35 +2206,35 @@
     <row r="14" spans="1:19" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A14" s="1"/>
       <c r="B14" s="38">
-        <f>ROW(B14) - ROW($B$9)</f>
+        <f t="shared" si="0"/>
         <v>5</v>
       </c>
       <c r="C14" s="59" t="s">
-        <v>143</v>
+        <v>133</v>
       </c>
       <c r="D14" s="46" t="s">
         <v>11</v>
       </c>
       <c r="E14" s="47" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="F14" s="46" t="s">
-        <v>65</v>
+        <v>58</v>
       </c>
       <c r="G14" s="47" t="s">
-        <v>182</v>
+        <v>170</v>
       </c>
       <c r="H14" s="46" t="s">
-        <v>203</v>
+        <v>191</v>
       </c>
       <c r="I14" s="46" t="s">
-        <v>187</v>
+        <v>175</v>
       </c>
       <c r="J14" s="46" t="s">
-        <v>157</v>
+        <v>147</v>
       </c>
       <c r="K14" s="46" t="s">
-        <v>119</v>
+        <v>110</v>
       </c>
       <c r="L14" s="47">
         <v>2</v>
@@ -2238,7 +2247,7 @@
         <v>50</v>
       </c>
       <c r="O14" s="61" t="s">
-        <v>178</v>
+        <v>166</v>
       </c>
       <c r="P14" s="53">
         <v>8.3999999999999995E-3</v>
@@ -2257,44 +2266,44 @@
         <v>6</v>
       </c>
       <c r="C15" s="60" t="s">
-        <v>143</v>
+        <v>133</v>
       </c>
       <c r="D15" s="50" t="s">
-        <v>12</v>
+        <v>194</v>
       </c>
       <c r="E15" s="51" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="F15" s="50" t="s">
-        <v>65</v>
+        <v>58</v>
       </c>
       <c r="G15" s="51" t="s">
-        <v>85</v>
+        <v>78</v>
       </c>
       <c r="H15" s="50" t="s">
-        <v>100</v>
+        <v>91</v>
       </c>
       <c r="I15" s="50" t="s">
-        <v>187</v>
+        <v>175</v>
       </c>
       <c r="J15" s="50" t="s">
-        <v>158</v>
+        <v>148</v>
       </c>
       <c r="K15" s="50" t="s">
-        <v>117</v>
+        <v>108</v>
       </c>
       <c r="L15" s="51">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="M15" s="50">
         <f t="shared" si="1"/>
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="N15" s="50">
         <v>100</v>
       </c>
       <c r="O15" s="62" t="s">
-        <v>178</v>
+        <v>166</v>
       </c>
       <c r="P15" s="54">
         <v>6.0000000000000001E-3</v>
@@ -2309,35 +2318,35 @@
     <row r="16" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A16" s="1"/>
       <c r="B16" s="38">
-        <f>ROW(B16) - ROW($B$9)</f>
+        <f t="shared" si="0"/>
         <v>7</v>
       </c>
       <c r="C16" s="59" t="s">
-        <v>143</v>
+        <v>133</v>
       </c>
       <c r="D16" s="46" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E16" s="47" t="s">
-        <v>42</v>
+        <v>195</v>
       </c>
       <c r="F16" s="46" t="s">
-        <v>65</v>
-      </c>
-      <c r="G16" s="47" t="s">
-        <v>86</v>
+        <v>58</v>
+      </c>
+      <c r="G16" s="64" t="s">
+        <v>196</v>
       </c>
       <c r="H16" s="46" t="s">
-        <v>100</v>
+        <v>197</v>
       </c>
       <c r="I16" s="46" t="s">
-        <v>187</v>
+        <v>198</v>
       </c>
       <c r="J16" s="46" t="s">
-        <v>159</v>
+        <v>204</v>
       </c>
       <c r="K16" s="46" t="s">
-        <v>120</v>
+        <v>199</v>
       </c>
       <c r="L16" s="47">
         <v>1</v>
@@ -2347,17 +2356,17 @@
         <v>10</v>
       </c>
       <c r="N16" s="46">
-        <v>50</v>
+        <v>20</v>
       </c>
       <c r="O16" s="61" t="s">
-        <v>178</v>
+        <v>166</v>
       </c>
       <c r="P16" s="53">
-        <v>1.3100000000000001E-2</v>
+        <v>4.7199999999999999E-2</v>
       </c>
       <c r="Q16" s="53">
         <f t="shared" si="2"/>
-        <v>0.65500000000000003</v>
+        <v>0.94399999999999995</v>
       </c>
       <c r="R16" s="48"/>
       <c r="S16" s="48"/>
@@ -2369,31 +2378,31 @@
         <v>8</v>
       </c>
       <c r="C17" s="60" t="s">
-        <v>143</v>
+        <v>133</v>
       </c>
       <c r="D17" s="50" t="s">
-        <v>14</v>
+        <v>200</v>
       </c>
       <c r="E17" s="51" t="s">
-        <v>43</v>
+        <v>201</v>
       </c>
       <c r="F17" s="50" t="s">
-        <v>67</v>
+        <v>58</v>
       </c>
       <c r="G17" s="51" t="s">
-        <v>87</v>
+        <v>202</v>
       </c>
       <c r="H17" s="50" t="s">
-        <v>103</v>
+        <v>203</v>
       </c>
       <c r="I17" s="50" t="s">
-        <v>187</v>
+        <v>175</v>
       </c>
       <c r="J17" s="50" t="s">
-        <v>160</v>
+        <v>205</v>
       </c>
       <c r="K17" s="50" t="s">
-        <v>121</v>
+        <v>108</v>
       </c>
       <c r="L17" s="51">
         <v>1</v>
@@ -2403,17 +2412,17 @@
         <v>10</v>
       </c>
       <c r="N17" s="50">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="O17" s="62" t="s">
-        <v>178</v>
+        <v>166</v>
       </c>
       <c r="P17" s="54">
-        <v>0.8125</v>
+        <v>2.7199999999999998E-2</v>
       </c>
       <c r="Q17" s="54">
-        <f t="shared" si="2"/>
-        <v>9.75</v>
+        <f>P17*N17</f>
+        <v>0.54399999999999993</v>
       </c>
       <c r="R17" s="52"/>
       <c r="S17" s="52"/>
@@ -2421,55 +2430,55 @@
     <row r="18" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A18" s="1"/>
       <c r="B18" s="38">
-        <f>ROW(B18) - ROW($B$9)</f>
+        <f t="shared" si="0"/>
         <v>9</v>
       </c>
       <c r="C18" s="59" t="s">
-        <v>143</v>
+        <v>133</v>
       </c>
       <c r="D18" s="46" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="E18" s="47" t="s">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="F18" s="46" t="s">
-        <v>68</v>
-      </c>
-      <c r="G18" s="66">
-        <v>885012205080</v>
+        <v>60</v>
+      </c>
+      <c r="G18" s="47" t="s">
+        <v>79</v>
       </c>
       <c r="H18" s="46" t="s">
-        <v>104</v>
+        <v>94</v>
       </c>
       <c r="I18" s="46" t="s">
-        <v>186</v>
+        <v>175</v>
       </c>
       <c r="J18" s="46" t="s">
-        <v>161</v>
+        <v>149</v>
       </c>
       <c r="K18" s="46" t="s">
-        <v>122</v>
+        <v>111</v>
       </c>
       <c r="L18" s="47">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M18" s="46">
         <f t="shared" si="1"/>
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="N18" s="46">
-        <v>100</v>
+        <v>12</v>
       </c>
       <c r="O18" s="61" t="s">
-        <v>178</v>
+        <v>166</v>
       </c>
       <c r="P18" s="53">
-        <v>4.5999999999999999E-3</v>
+        <v>0.8125</v>
       </c>
       <c r="Q18" s="53">
         <f t="shared" si="2"/>
-        <v>0.45999999999999996</v>
+        <v>9.75</v>
       </c>
       <c r="R18" s="48"/>
       <c r="S18" s="48"/>
@@ -2481,87 +2490,87 @@
         <v>10</v>
       </c>
       <c r="C19" s="60" t="s">
-        <v>144</v>
+        <v>133</v>
       </c>
       <c r="D19" s="50" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="E19" s="51" t="s">
-        <v>45</v>
+        <v>38</v>
       </c>
       <c r="F19" s="50" t="s">
-        <v>69</v>
-      </c>
-      <c r="G19" s="51" t="s">
-        <v>88</v>
+        <v>61</v>
+      </c>
+      <c r="G19" s="63">
+        <v>885012205080</v>
       </c>
       <c r="H19" s="50" t="s">
-        <v>105</v>
+        <v>95</v>
       </c>
       <c r="I19" s="50" t="s">
-        <v>187</v>
+        <v>174</v>
       </c>
       <c r="J19" s="50" t="s">
-        <v>162</v>
+        <v>150</v>
       </c>
       <c r="K19" s="50" t="s">
-        <v>187</v>
+        <v>112</v>
       </c>
       <c r="L19" s="51">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M19" s="50">
         <f t="shared" si="1"/>
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="N19" s="50">
-        <v>20</v>
+        <v>100</v>
       </c>
       <c r="O19" s="62" t="s">
-        <v>178</v>
+        <v>166</v>
       </c>
       <c r="P19" s="54">
-        <v>4.3099999999999999E-2</v>
+        <v>4.5999999999999999E-3</v>
       </c>
       <c r="Q19" s="54">
         <f t="shared" si="2"/>
-        <v>0.86199999999999999</v>
+        <v>0.45999999999999996</v>
       </c>
       <c r="R19" s="52"/>
       <c r="S19" s="52"/>
     </row>
-    <row r="20" spans="1:19" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A20" s="1"/>
       <c r="B20" s="38">
-        <f>ROW(B20) - ROW($B$9)</f>
+        <f t="shared" si="0"/>
         <v>11</v>
       </c>
       <c r="C20" s="59" t="s">
-        <v>145</v>
+        <v>134</v>
       </c>
       <c r="D20" s="46" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="E20" s="47" t="s">
-        <v>46</v>
+        <v>39</v>
       </c>
       <c r="F20" s="46" t="s">
-        <v>70</v>
+        <v>62</v>
       </c>
       <c r="G20" s="47" t="s">
-        <v>183</v>
+        <v>80</v>
       </c>
       <c r="H20" s="46" t="s">
-        <v>204</v>
+        <v>96</v>
       </c>
       <c r="I20" s="46" t="s">
-        <v>187</v>
+        <v>175</v>
       </c>
       <c r="J20" s="46" t="s">
-        <v>163</v>
+        <v>151</v>
       </c>
       <c r="K20" s="46" t="s">
-        <v>123</v>
+        <v>175</v>
       </c>
       <c r="L20" s="47">
         <v>1</v>
@@ -2571,17 +2580,17 @@
         <v>10</v>
       </c>
       <c r="N20" s="46">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="O20" s="61" t="s">
-        <v>178</v>
+        <v>166</v>
       </c>
       <c r="P20" s="53">
-        <v>0.18379999999999999</v>
+        <v>4.3099999999999999E-2</v>
       </c>
       <c r="Q20" s="53">
         <f t="shared" si="2"/>
-        <v>2.7569999999999997</v>
+        <v>0.86199999999999999</v>
       </c>
       <c r="R20" s="48"/>
       <c r="S20" s="48"/>
@@ -2593,31 +2602,31 @@
         <v>12</v>
       </c>
       <c r="C21" s="60" t="s">
-        <v>145</v>
+        <v>135</v>
       </c>
       <c r="D21" s="50" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="E21" s="51" t="s">
-        <v>47</v>
+        <v>40</v>
       </c>
       <c r="F21" s="50" t="s">
-        <v>70</v>
+        <v>63</v>
       </c>
       <c r="G21" s="51" t="s">
-        <v>184</v>
+        <v>171</v>
       </c>
       <c r="H21" s="50" t="s">
-        <v>205</v>
+        <v>192</v>
       </c>
       <c r="I21" s="50" t="s">
-        <v>187</v>
+        <v>175</v>
       </c>
       <c r="J21" s="50" t="s">
-        <v>164</v>
+        <v>152</v>
       </c>
       <c r="K21" s="50" t="s">
-        <v>124</v>
+        <v>113</v>
       </c>
       <c r="L21" s="51">
         <v>1</v>
@@ -2627,51 +2636,53 @@
         <v>10</v>
       </c>
       <c r="N21" s="50">
-        <v>50</v>
+        <v>15</v>
       </c>
       <c r="O21" s="62" t="s">
-        <v>178</v>
+        <v>166</v>
       </c>
       <c r="P21" s="54">
-        <v>1.5599999999999999E-2</v>
+        <v>0.18379999999999999</v>
       </c>
       <c r="Q21" s="54">
         <f t="shared" si="2"/>
-        <v>0.77999999999999992</v>
+        <v>2.7569999999999997</v>
       </c>
       <c r="R21" s="52"/>
       <c r="S21" s="52"/>
     </row>
-    <row r="22" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:19" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A22" s="1"/>
       <c r="B22" s="38">
-        <f>ROW(B22) - ROW($B$9)</f>
+        <f t="shared" si="0"/>
         <v>13</v>
       </c>
       <c r="C22" s="59" t="s">
-        <v>145</v>
+        <v>135</v>
       </c>
       <c r="D22" s="46" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="E22" s="47" t="s">
-        <v>48</v>
-      </c>
-      <c r="F22" s="46"/>
+        <v>41</v>
+      </c>
+      <c r="F22" s="46" t="s">
+        <v>63</v>
+      </c>
       <c r="G22" s="47" t="s">
-        <v>89</v>
+        <v>172</v>
       </c>
       <c r="H22" s="46" t="s">
-        <v>106</v>
+        <v>193</v>
       </c>
       <c r="I22" s="46" t="s">
-        <v>187</v>
+        <v>175</v>
       </c>
       <c r="J22" s="46" t="s">
-        <v>165</v>
+        <v>153</v>
       </c>
       <c r="K22" s="46" t="s">
-        <v>125</v>
+        <v>114</v>
       </c>
       <c r="L22" s="47">
         <v>1</v>
@@ -2681,53 +2692,51 @@
         <v>10</v>
       </c>
       <c r="N22" s="46">
-        <v>15</v>
+        <v>50</v>
       </c>
       <c r="O22" s="61" t="s">
-        <v>178</v>
+        <v>166</v>
       </c>
       <c r="P22" s="53">
-        <v>9.7900000000000001E-2</v>
+        <v>1.5599999999999999E-2</v>
       </c>
       <c r="Q22" s="53">
         <f t="shared" si="2"/>
-        <v>1.4684999999999999</v>
+        <v>0.77999999999999992</v>
       </c>
       <c r="R22" s="48"/>
       <c r="S22" s="48"/>
     </row>
-    <row r="23" spans="1:19" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A23" s="1"/>
       <c r="B23" s="38">
         <f t="shared" si="0"/>
         <v>14</v>
       </c>
       <c r="C23" s="60" t="s">
-        <v>146</v>
+        <v>135</v>
       </c>
       <c r="D23" s="50" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="E23" s="51" t="s">
-        <v>49</v>
-      </c>
-      <c r="F23" s="50" t="s">
-        <v>71</v>
-      </c>
+        <v>42</v>
+      </c>
+      <c r="F23" s="50"/>
       <c r="G23" s="51" t="s">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="H23" s="50" t="s">
-        <v>107</v>
+        <v>97</v>
       </c>
       <c r="I23" s="50" t="s">
-        <v>187</v>
+        <v>175</v>
       </c>
       <c r="J23" s="50" t="s">
-        <v>166</v>
+        <v>154</v>
       </c>
       <c r="K23" s="50" t="s">
-        <v>126</v>
+        <v>115</v>
       </c>
       <c r="L23" s="51">
         <v>1</v>
@@ -2737,17 +2746,17 @@
         <v>10</v>
       </c>
       <c r="N23" s="50">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="O23" s="62" t="s">
-        <v>178</v>
+        <v>166</v>
       </c>
       <c r="P23" s="54">
-        <v>4.2099999999999999E-2</v>
+        <v>9.7900000000000001E-2</v>
       </c>
       <c r="Q23" s="54">
         <f t="shared" si="2"/>
-        <v>0.84199999999999997</v>
+        <v>1.4684999999999999</v>
       </c>
       <c r="R23" s="52"/>
       <c r="S23" s="52"/>
@@ -2755,35 +2764,35 @@
     <row r="24" spans="1:19" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A24" s="1"/>
       <c r="B24" s="38">
-        <f>ROW(B24) - ROW($B$9)</f>
+        <f t="shared" si="0"/>
         <v>15</v>
       </c>
       <c r="C24" s="59" t="s">
-        <v>146</v>
+        <v>136</v>
       </c>
       <c r="D24" s="46" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="E24" s="47" t="s">
-        <v>50</v>
+        <v>43</v>
       </c>
       <c r="F24" s="46" t="s">
-        <v>72</v>
+        <v>64</v>
       </c>
       <c r="G24" s="47" t="s">
-        <v>91</v>
+        <v>82</v>
       </c>
       <c r="H24" s="46" t="s">
-        <v>108</v>
+        <v>98</v>
       </c>
       <c r="I24" s="46" t="s">
-        <v>187</v>
+        <v>175</v>
       </c>
       <c r="J24" s="46" t="s">
-        <v>167</v>
+        <v>155</v>
       </c>
       <c r="K24" s="46" t="s">
-        <v>127</v>
+        <v>116</v>
       </c>
       <c r="L24" s="47">
         <v>1</v>
@@ -2796,70 +2805,70 @@
         <v>20</v>
       </c>
       <c r="O24" s="61" t="s">
-        <v>178</v>
+        <v>166</v>
       </c>
       <c r="P24" s="53">
-        <v>6.93E-2</v>
+        <v>4.2099999999999999E-2</v>
       </c>
       <c r="Q24" s="53">
         <f t="shared" si="2"/>
-        <v>1.3860000000000001</v>
+        <v>0.84199999999999997</v>
       </c>
       <c r="R24" s="48"/>
       <c r="S24" s="48"/>
     </row>
-    <row r="25" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:19" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A25" s="1"/>
       <c r="B25" s="38">
         <f t="shared" si="0"/>
         <v>16</v>
       </c>
       <c r="C25" s="60" t="s">
-        <v>147</v>
+        <v>136</v>
       </c>
       <c r="D25" s="50" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="E25" s="51" t="s">
-        <v>51</v>
+        <v>44</v>
       </c>
       <c r="F25" s="50" t="s">
-        <v>189</v>
+        <v>65</v>
       </c>
       <c r="G25" s="51" t="s">
-        <v>73</v>
+        <v>83</v>
       </c>
       <c r="H25" s="50" t="s">
-        <v>109</v>
+        <v>99</v>
       </c>
       <c r="I25" s="50" t="s">
-        <v>187</v>
+        <v>175</v>
       </c>
       <c r="J25" s="50" t="s">
-        <v>168</v>
+        <v>156</v>
       </c>
       <c r="K25" s="50" t="s">
-        <v>187</v>
+        <v>117</v>
       </c>
       <c r="L25" s="51">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M25" s="50">
         <f t="shared" si="1"/>
+        <v>10</v>
+      </c>
+      <c r="N25" s="50">
         <v>20</v>
       </c>
-      <c r="N25" s="50">
-        <v>25</v>
-      </c>
       <c r="O25" s="62" t="s">
-        <v>178</v>
+        <v>166</v>
       </c>
       <c r="P25" s="54">
-        <v>0.1351</v>
+        <v>6.93E-2</v>
       </c>
       <c r="Q25" s="54">
         <f t="shared" si="2"/>
-        <v>3.3774999999999999</v>
+        <v>1.3860000000000001</v>
       </c>
       <c r="R25" s="52"/>
       <c r="S25" s="52"/>
@@ -2867,35 +2876,35 @@
     <row r="26" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A26" s="1"/>
       <c r="B26" s="38">
-        <f>ROW(B26) - ROW($B$9)</f>
+        <f t="shared" si="0"/>
         <v>17</v>
       </c>
       <c r="C26" s="59" t="s">
-        <v>148</v>
+        <v>137</v>
       </c>
       <c r="D26" s="46" t="s">
-        <v>23</v>
+        <v>213</v>
       </c>
       <c r="E26" s="47" t="s">
-        <v>52</v>
+        <v>45</v>
       </c>
       <c r="F26" s="46" t="s">
-        <v>74</v>
-      </c>
-      <c r="G26" s="66">
-        <v>61300611121</v>
+        <v>177</v>
+      </c>
+      <c r="G26" s="47" t="s">
+        <v>66</v>
       </c>
       <c r="H26" s="46" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="I26" s="46" t="s">
-        <v>201</v>
+        <v>175</v>
       </c>
       <c r="J26" s="46" t="s">
-        <v>202</v>
+        <v>157</v>
       </c>
       <c r="K26" s="46" t="s">
-        <v>187</v>
+        <v>175</v>
       </c>
       <c r="L26" s="47">
         <v>2</v>
@@ -2905,109 +2914,109 @@
         <v>20</v>
       </c>
       <c r="N26" s="46">
-        <v>40</v>
+        <v>25</v>
       </c>
       <c r="O26" s="61" t="s">
-        <v>178</v>
+        <v>166</v>
       </c>
       <c r="P26" s="53">
-        <v>2.6800000000000001E-2</v>
+        <v>0.1351</v>
       </c>
       <c r="Q26" s="53">
         <f t="shared" si="2"/>
-        <v>1.0720000000000001</v>
+        <v>3.3774999999999999</v>
       </c>
       <c r="R26" s="48"/>
       <c r="S26" s="48"/>
     </row>
-    <row r="27" spans="1:19" ht="48.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A27" s="1"/>
       <c r="B27" s="38">
         <f t="shared" si="0"/>
         <v>18</v>
       </c>
       <c r="C27" s="60" t="s">
-        <v>149</v>
+        <v>138</v>
       </c>
       <c r="D27" s="50" t="s">
-        <v>24</v>
+        <v>214</v>
       </c>
       <c r="E27" s="51" t="s">
-        <v>53</v>
+        <v>46</v>
       </c>
       <c r="F27" s="50" t="s">
-        <v>75</v>
-      </c>
-      <c r="G27" s="51" t="s">
-        <v>128</v>
+        <v>67</v>
+      </c>
+      <c r="G27" s="63">
+        <v>61300611121</v>
       </c>
       <c r="H27" s="50" t="s">
-        <v>195</v>
+        <v>95</v>
       </c>
       <c r="I27" s="50" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="J27" s="50" t="s">
-        <v>169</v>
+        <v>190</v>
       </c>
       <c r="K27" s="50" t="s">
-        <v>187</v>
+        <v>175</v>
       </c>
       <c r="L27" s="51">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M27" s="50">
         <f t="shared" si="1"/>
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="N27" s="50">
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="O27" s="62" t="s">
-        <v>178</v>
+        <v>166</v>
       </c>
       <c r="P27" s="54">
-        <v>2.1899999999999999E-2</v>
+        <v>2.6800000000000001E-2</v>
       </c>
       <c r="Q27" s="54">
         <f t="shared" si="2"/>
-        <v>0.438</v>
+        <v>1.0720000000000001</v>
       </c>
       <c r="R27" s="52"/>
       <c r="S27" s="52"/>
     </row>
-    <row r="28" spans="1:19" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:19" ht="48.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A28" s="1"/>
       <c r="B28" s="38">
-        <f>ROW(B28) - ROW($B$9)</f>
+        <f t="shared" si="0"/>
         <v>19</v>
       </c>
       <c r="C28" s="59" t="s">
-        <v>149</v>
+        <v>139</v>
       </c>
       <c r="D28" s="46" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="E28" s="47" t="s">
-        <v>54</v>
+        <v>47</v>
       </c>
       <c r="F28" s="46" t="s">
-        <v>76</v>
+        <v>68</v>
       </c>
       <c r="G28" s="47" t="s">
-        <v>129</v>
+        <v>118</v>
       </c>
       <c r="H28" s="46" t="s">
-        <v>194</v>
+        <v>183</v>
       </c>
       <c r="I28" s="46" t="s">
-        <v>187</v>
+        <v>175</v>
       </c>
       <c r="J28" s="46" t="s">
-        <v>170</v>
+        <v>158</v>
       </c>
       <c r="K28" s="46" t="s">
-        <v>187</v>
+        <v>175</v>
       </c>
       <c r="L28" s="47">
         <v>1</v>
@@ -3017,53 +3026,53 @@
         <v>10</v>
       </c>
       <c r="N28" s="46">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="O28" s="61" t="s">
-        <v>178</v>
+        <v>166</v>
       </c>
       <c r="P28" s="53">
-        <v>0.20269999999999999</v>
+        <v>2.1899999999999999E-2</v>
       </c>
       <c r="Q28" s="53">
         <f t="shared" si="2"/>
-        <v>3.0404999999999998</v>
+        <v>0.438</v>
       </c>
       <c r="R28" s="48"/>
       <c r="S28" s="48"/>
     </row>
-    <row r="29" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:19" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A29" s="1"/>
       <c r="B29" s="38">
         <f t="shared" si="0"/>
         <v>20</v>
       </c>
       <c r="C29" s="60" t="s">
-        <v>150</v>
+        <v>139</v>
       </c>
       <c r="D29" s="50" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="E29" s="51" t="s">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="F29" s="50" t="s">
-        <v>77</v>
-      </c>
-      <c r="G29" s="65" t="s">
-        <v>185</v>
+        <v>69</v>
+      </c>
+      <c r="G29" s="51" t="s">
+        <v>119</v>
       </c>
       <c r="H29" s="50" t="s">
-        <v>110</v>
+        <v>182</v>
       </c>
       <c r="I29" s="50" t="s">
-        <v>196</v>
+        <v>175</v>
       </c>
       <c r="J29" s="50" t="s">
-        <v>171</v>
+        <v>159</v>
       </c>
       <c r="K29" s="50" t="s">
-        <v>130</v>
+        <v>175</v>
       </c>
       <c r="L29" s="51">
         <v>1</v>
@@ -3073,129 +3082,129 @@
         <v>10</v>
       </c>
       <c r="N29" s="50">
-        <v>100</v>
+        <v>15</v>
       </c>
       <c r="O29" s="62" t="s">
-        <v>178</v>
+        <v>166</v>
       </c>
       <c r="P29" s="54">
-        <v>1.4E-3</v>
+        <v>0.20269999999999999</v>
       </c>
       <c r="Q29" s="54">
         <f t="shared" si="2"/>
-        <v>0.13999999999999999</v>
+        <v>3.0404999999999998</v>
       </c>
       <c r="R29" s="52"/>
       <c r="S29" s="52"/>
     </row>
-    <row r="30" spans="1:19" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A30" s="1"/>
       <c r="B30" s="38">
-        <f>ROW(B30) - ROW($B$9)</f>
+        <f t="shared" si="0"/>
         <v>21</v>
       </c>
       <c r="C30" s="59" t="s">
-        <v>150</v>
+        <v>140</v>
       </c>
       <c r="D30" s="46" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="E30" s="47" t="s">
-        <v>56</v>
+        <v>49</v>
       </c>
       <c r="F30" s="46" t="s">
-        <v>77</v>
-      </c>
-      <c r="G30" s="47" t="s">
-        <v>92</v>
+        <v>70</v>
+      </c>
+      <c r="G30" s="64" t="s">
+        <v>173</v>
       </c>
       <c r="H30" s="46" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="I30" s="46" t="s">
-        <v>187</v>
+        <v>184</v>
       </c>
       <c r="J30" s="46" t="s">
-        <v>172</v>
+        <v>160</v>
       </c>
       <c r="K30" s="46" t="s">
-        <v>131</v>
+        <v>120</v>
       </c>
       <c r="L30" s="47">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="M30" s="46">
         <f t="shared" si="1"/>
-        <v>80</v>
+        <v>10</v>
       </c>
       <c r="N30" s="46">
         <v>100</v>
       </c>
       <c r="O30" s="61" t="s">
-        <v>178</v>
+        <v>166</v>
       </c>
       <c r="P30" s="53">
-        <v>1.6999999999999999E-3</v>
+        <v>1.4E-3</v>
       </c>
       <c r="Q30" s="53">
         <f t="shared" si="2"/>
-        <v>0.16999999999999998</v>
+        <v>0.13999999999999999</v>
       </c>
       <c r="R30" s="48"/>
       <c r="S30" s="48"/>
     </row>
-    <row r="31" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:19" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A31" s="1"/>
       <c r="B31" s="38">
         <f t="shared" si="0"/>
         <v>22</v>
       </c>
       <c r="C31" s="60" t="s">
-        <v>150</v>
+        <v>140</v>
       </c>
       <c r="D31" s="50" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="E31" s="51" t="s">
-        <v>57</v>
+        <v>50</v>
       </c>
       <c r="F31" s="50" t="s">
-        <v>78</v>
-      </c>
-      <c r="G31" s="65" t="s">
-        <v>93</v>
+        <v>70</v>
+      </c>
+      <c r="G31" s="51" t="s">
+        <v>84</v>
       </c>
       <c r="H31" s="50" t="s">
-        <v>111</v>
+        <v>91</v>
       </c>
       <c r="I31" s="50" t="s">
-        <v>197</v>
+        <v>175</v>
       </c>
       <c r="J31" s="50" t="s">
-        <v>173</v>
+        <v>161</v>
       </c>
       <c r="K31" s="50" t="s">
-        <v>132</v>
+        <v>121</v>
       </c>
       <c r="L31" s="51">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="M31" s="50">
         <f t="shared" si="1"/>
-        <v>10</v>
+        <v>80</v>
       </c>
       <c r="N31" s="50">
         <v>100</v>
       </c>
       <c r="O31" s="62" t="s">
-        <v>178</v>
+        <v>166</v>
       </c>
       <c r="P31" s="54">
-        <v>6.9999999999999999E-4</v>
+        <v>1.6999999999999999E-3</v>
       </c>
       <c r="Q31" s="54">
         <f t="shared" si="2"/>
-        <v>6.9999999999999993E-2</v>
+        <v>0.16999999999999998</v>
       </c>
       <c r="R31" s="52"/>
       <c r="S31" s="52"/>
@@ -3203,35 +3212,35 @@
     <row r="32" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A32" s="1"/>
       <c r="B32" s="38">
-        <f>ROW(B32) - ROW($B$9)</f>
+        <f t="shared" si="0"/>
         <v>23</v>
       </c>
       <c r="C32" s="59" t="s">
-        <v>150</v>
+        <v>140</v>
       </c>
       <c r="D32" s="46" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="E32" s="47" t="s">
-        <v>58</v>
+        <v>51</v>
       </c>
       <c r="F32" s="46" t="s">
-        <v>77</v>
-      </c>
-      <c r="G32" s="47" t="s">
-        <v>94</v>
+        <v>71</v>
+      </c>
+      <c r="G32" s="64" t="s">
+        <v>85</v>
       </c>
       <c r="H32" s="46" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="I32" s="46" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="J32" s="46" t="s">
-        <v>174</v>
+        <v>162</v>
       </c>
       <c r="K32" s="46" t="s">
-        <v>133</v>
+        <v>122</v>
       </c>
       <c r="L32" s="47">
         <v>1</v>
@@ -3244,63 +3253,63 @@
         <v>100</v>
       </c>
       <c r="O32" s="61" t="s">
-        <v>178</v>
+        <v>166</v>
       </c>
       <c r="P32" s="53">
-        <v>1E-3</v>
+        <v>6.9999999999999999E-4</v>
       </c>
       <c r="Q32" s="53">
         <f t="shared" si="2"/>
-        <v>0.1</v>
+        <v>6.9999999999999993E-2</v>
       </c>
       <c r="R32" s="48"/>
       <c r="S32" s="48"/>
     </row>
-    <row r="33" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:19" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A33" s="1"/>
       <c r="B33" s="38">
         <f t="shared" si="0"/>
         <v>24</v>
       </c>
       <c r="C33" s="60" t="s">
-        <v>150</v>
+        <v>140</v>
       </c>
       <c r="D33" s="50" t="s">
-        <v>30</v>
+        <v>206</v>
       </c>
       <c r="E33" s="51" t="s">
-        <v>59</v>
+        <v>52</v>
       </c>
       <c r="F33" s="50" t="s">
-        <v>77</v>
+        <v>70</v>
       </c>
       <c r="G33" s="51" t="s">
-        <v>95</v>
+        <v>86</v>
       </c>
       <c r="H33" s="50" t="s">
-        <v>100</v>
+        <v>91</v>
       </c>
       <c r="I33" s="50" t="s">
-        <v>187</v>
+        <v>175</v>
       </c>
       <c r="J33" s="50" t="s">
-        <v>175</v>
+        <v>163</v>
       </c>
       <c r="K33" s="50" t="s">
-        <v>134</v>
+        <v>124</v>
       </c>
       <c r="L33" s="51">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="M33" s="50">
         <f t="shared" si="1"/>
-        <v>40</v>
+        <v>70</v>
       </c>
       <c r="N33" s="50">
         <v>100</v>
       </c>
       <c r="O33" s="62" t="s">
-        <v>178</v>
+        <v>166</v>
       </c>
       <c r="P33" s="54">
         <v>1.1999999999999999E-3</v>
@@ -3312,212 +3321,214 @@
       <c r="R33" s="52"/>
       <c r="S33" s="52"/>
     </row>
-    <row r="34" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:19" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A34" s="1"/>
       <c r="B34" s="38">
-        <f>ROW(B34) - ROW($B$9)</f>
+        <f t="shared" si="0"/>
         <v>25</v>
       </c>
       <c r="C34" s="59" t="s">
-        <v>79</v>
+        <v>140</v>
       </c>
       <c r="D34" s="46" t="s">
-        <v>31</v>
+        <v>207</v>
       </c>
       <c r="E34" s="47" t="s">
-        <v>60</v>
+        <v>208</v>
       </c>
       <c r="F34" s="46" t="s">
-        <v>187</v>
+        <v>209</v>
       </c>
       <c r="G34" s="47" t="s">
-        <v>187</v>
+        <v>210</v>
       </c>
       <c r="H34" s="46" t="s">
-        <v>187</v>
+        <v>211</v>
       </c>
       <c r="I34" s="46" t="s">
-        <v>187</v>
+        <v>175</v>
       </c>
       <c r="J34" s="46" t="s">
-        <v>187</v>
+        <v>212</v>
       </c>
       <c r="K34" s="46" t="s">
-        <v>187</v>
+        <v>123</v>
       </c>
       <c r="L34" s="47">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="M34" s="46">
         <f t="shared" si="1"/>
-        <v>50</v>
-      </c>
-      <c r="N34" s="46" t="s">
-        <v>187</v>
-      </c>
-      <c r="O34" s="46" t="s">
-        <v>187</v>
-      </c>
-      <c r="P34" s="53" t="s">
-        <v>187</v>
-      </c>
-      <c r="Q34" s="53" t="s">
-        <v>187</v>
-      </c>
-      <c r="R34" s="64" t="s">
-        <v>188</v>
-      </c>
-      <c r="S34" s="53" t="s">
-        <v>187</v>
-      </c>
-    </row>
-    <row r="35" spans="1:19" ht="48.75" thickBot="1" x14ac:dyDescent="0.3">
+        <v>10</v>
+      </c>
+      <c r="N34" s="46">
+        <v>20</v>
+      </c>
+      <c r="O34" s="61" t="s">
+        <v>166</v>
+      </c>
+      <c r="P34" s="53">
+        <v>6.4399999999999999E-2</v>
+      </c>
+      <c r="Q34" s="53">
+        <f>P34*N34</f>
+        <v>1.288</v>
+      </c>
+      <c r="R34" s="48"/>
+      <c r="S34" s="48"/>
+    </row>
+    <row r="35" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A35" s="1"/>
       <c r="B35" s="38">
         <f t="shared" si="0"/>
         <v>26</v>
       </c>
       <c r="C35" s="60" t="s">
-        <v>151</v>
+        <v>72</v>
       </c>
       <c r="D35" s="50" t="s">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="E35" s="51" t="s">
-        <v>61</v>
+        <v>53</v>
       </c>
       <c r="F35" s="50" t="s">
-        <v>189</v>
+        <v>175</v>
       </c>
       <c r="G35" s="51" t="s">
-        <v>96</v>
+        <v>175</v>
       </c>
       <c r="H35" s="50" t="s">
-        <v>112</v>
+        <v>175</v>
       </c>
       <c r="I35" s="50" t="s">
-        <v>187</v>
+        <v>175</v>
       </c>
       <c r="J35" s="50" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="K35" s="50" t="s">
-        <v>187</v>
+        <v>175</v>
       </c>
       <c r="L35" s="51">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="M35" s="50">
         <f t="shared" si="1"/>
+        <v>50</v>
+      </c>
+      <c r="N35" s="50" t="s">
+        <v>175</v>
+      </c>
+      <c r="O35" s="62" t="s">
+        <v>175</v>
+      </c>
+      <c r="P35" s="54" t="s">
+        <v>175</v>
+      </c>
+      <c r="Q35" s="54" t="s">
+        <v>175</v>
+      </c>
+      <c r="R35" s="77" t="s">
+        <v>176</v>
+      </c>
+      <c r="S35" s="52" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="36" spans="1:19" ht="48.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A36" s="1"/>
+      <c r="B36" s="38">
+        <f t="shared" si="0"/>
+        <v>27</v>
+      </c>
+      <c r="C36" s="59" t="s">
+        <v>141</v>
+      </c>
+      <c r="D36" s="46" t="s">
+        <v>27</v>
+      </c>
+      <c r="E36" s="47" t="s">
+        <v>54</v>
+      </c>
+      <c r="F36" s="46" t="s">
+        <v>177</v>
+      </c>
+      <c r="G36" s="47" t="s">
+        <v>87</v>
+      </c>
+      <c r="H36" s="46" t="s">
+        <v>103</v>
+      </c>
+      <c r="I36" s="46" t="s">
+        <v>175</v>
+      </c>
+      <c r="J36" s="46" t="s">
+        <v>164</v>
+      </c>
+      <c r="K36" s="46" t="s">
+        <v>175</v>
+      </c>
+      <c r="L36" s="47">
+        <v>3</v>
+      </c>
+      <c r="M36" s="46">
+        <f t="shared" si="1"/>
         <v>30</v>
       </c>
-      <c r="N35" s="50">
+      <c r="N36" s="46">
         <v>33</v>
       </c>
-      <c r="O35" s="62" t="s">
-        <v>178</v>
-      </c>
-      <c r="P35" s="54">
+      <c r="O36" s="61" t="s">
+        <v>166</v>
+      </c>
+      <c r="P36" s="53">
         <v>0.2752</v>
       </c>
-      <c r="Q35" s="54">
+      <c r="Q36" s="53">
         <f t="shared" si="2"/>
         <v>9.0815999999999999</v>
       </c>
-      <c r="R35" s="52"/>
-      <c r="S35" s="52"/>
-    </row>
-    <row r="36" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A36" s="1"/>
-      <c r="B36" s="38">
-        <f>ROW(B36) - ROW($B$9)</f>
-        <v>27</v>
-      </c>
-      <c r="C36" s="59" t="s">
-        <v>152</v>
-      </c>
-      <c r="D36" s="46" t="s">
-        <v>33</v>
-      </c>
-      <c r="E36" s="47" t="s">
-        <v>62</v>
-      </c>
-      <c r="F36" s="46" t="s">
-        <v>76</v>
-      </c>
-      <c r="G36" s="47" t="s">
-        <v>97</v>
-      </c>
-      <c r="H36" s="46" t="s">
-        <v>113</v>
-      </c>
-      <c r="I36" s="46" t="s">
-        <v>187</v>
-      </c>
-      <c r="J36" s="46" t="s">
-        <v>177</v>
-      </c>
-      <c r="K36" s="46" t="s">
-        <v>187</v>
-      </c>
-      <c r="L36" s="47">
-        <v>1</v>
-      </c>
-      <c r="M36" s="46">
-        <f t="shared" si="1"/>
-        <v>10</v>
-      </c>
-      <c r="N36" s="46">
-        <v>11</v>
-      </c>
-      <c r="O36" s="61" t="s">
-        <v>178</v>
-      </c>
-      <c r="P36" s="53">
-        <v>2.4839000000000002</v>
-      </c>
-      <c r="Q36" s="53">
-        <f t="shared" si="2"/>
-        <v>27.322900000000004</v>
-      </c>
       <c r="R36" s="48"/>
       <c r="S36" s="48"/>
     </row>
-    <row r="37" spans="1:19" ht="45.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A37" s="1"/>
       <c r="B37" s="38">
         <f t="shared" si="0"/>
         <v>28</v>
       </c>
       <c r="C37" s="60" t="s">
-        <v>152</v>
+        <v>142</v>
       </c>
       <c r="D37" s="50" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="E37" s="51" t="s">
-        <v>63</v>
+        <v>55</v>
       </c>
       <c r="F37" s="50" t="s">
-        <v>80</v>
+        <v>69</v>
       </c>
       <c r="G37" s="51" t="s">
-        <v>98</v>
+        <v>88</v>
       </c>
       <c r="H37" s="50" t="s">
-        <v>114</v>
+        <v>104</v>
       </c>
       <c r="I37" s="50" t="s">
-        <v>187</v>
-      </c>
-      <c r="J37" s="50"/>
+        <v>175</v>
+      </c>
+      <c r="J37" s="50" t="s">
+        <v>165</v>
+      </c>
       <c r="K37" s="50" t="s">
-        <v>187</v>
+        <v>175</v>
       </c>
       <c r="L37" s="51">
         <v>1</v>
       </c>
-      <c r="M37" s="63">
+      <c r="M37" s="50">
         <f t="shared" si="1"/>
         <v>10</v>
       </c>
@@ -3525,77 +3536,131 @@
         <v>11</v>
       </c>
       <c r="O37" s="62" t="s">
-        <v>200</v>
+        <v>166</v>
       </c>
       <c r="P37" s="54">
-        <v>5.15</v>
+        <v>2.4839000000000002</v>
       </c>
       <c r="Q37" s="54">
         <f t="shared" si="2"/>
-        <v>56.650000000000006</v>
+        <v>27.322900000000004</v>
       </c>
       <c r="R37" s="52"/>
       <c r="S37" s="52"/>
     </row>
-    <row r="38" spans="1:19" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:19" ht="45.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A38" s="1"/>
-      <c r="B38" s="33"/>
-      <c r="C38" s="44"/>
-      <c r="D38" s="34"/>
-      <c r="E38" s="35"/>
-      <c r="F38" s="36"/>
-      <c r="G38" s="37"/>
-      <c r="H38" s="36"/>
-      <c r="I38" s="37"/>
-      <c r="J38" s="36"/>
-      <c r="K38" s="37"/>
-      <c r="L38" s="37"/>
-      <c r="M38" s="37"/>
-      <c r="N38" s="77" t="s">
-        <v>198</v>
-      </c>
-      <c r="O38" s="78"/>
-      <c r="P38" s="78"/>
-      <c r="Q38" s="67">
-        <f>SUM(Q10:Q37)</f>
-        <v>130.74640000000002</v>
-      </c>
-      <c r="R38" s="73"/>
-      <c r="S38" s="74"/>
+      <c r="B38" s="38">
+        <f t="shared" si="0"/>
+        <v>29</v>
+      </c>
+      <c r="C38" s="59" t="s">
+        <v>142</v>
+      </c>
+      <c r="D38" s="46" t="s">
+        <v>29</v>
+      </c>
+      <c r="E38" s="47" t="s">
+        <v>56</v>
+      </c>
+      <c r="F38" s="46" t="s">
+        <v>73</v>
+      </c>
+      <c r="G38" s="47" t="s">
+        <v>89</v>
+      </c>
+      <c r="H38" s="46" t="s">
+        <v>105</v>
+      </c>
+      <c r="I38" s="46" t="s">
+        <v>175</v>
+      </c>
+      <c r="J38" s="46"/>
+      <c r="K38" s="46" t="s">
+        <v>175</v>
+      </c>
+      <c r="L38" s="47">
+        <v>1</v>
+      </c>
+      <c r="M38" s="46">
+        <f t="shared" si="1"/>
+        <v>10</v>
+      </c>
+      <c r="N38" s="46">
+        <v>11</v>
+      </c>
+      <c r="O38" s="61" t="s">
+        <v>188</v>
+      </c>
+      <c r="P38" s="53">
+        <v>5.15</v>
+      </c>
+      <c r="Q38" s="53">
+        <f t="shared" si="2"/>
+        <v>56.650000000000006</v>
+      </c>
+      <c r="R38" s="48"/>
+      <c r="S38" s="48"/>
     </row>
     <row r="39" spans="1:19" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A39" s="1"/>
-      <c r="B39" s="25"/>
-      <c r="C39" s="45"/>
-      <c r="D39" s="9"/>
-      <c r="E39" s="10"/>
-      <c r="F39" s="10"/>
-      <c r="G39" s="10"/>
-      <c r="H39" s="10"/>
-      <c r="I39" s="10"/>
-      <c r="J39" s="10"/>
-      <c r="K39" s="10"/>
-      <c r="L39" s="10"/>
-      <c r="M39" s="10"/>
-      <c r="N39" s="77" t="s">
-        <v>199</v>
-      </c>
-      <c r="O39" s="78"/>
-      <c r="P39" s="78"/>
-      <c r="Q39" s="68">
-        <f>Q38/10</f>
-        <v>13.074640000000002</v>
-      </c>
-      <c r="R39" s="75"/>
-      <c r="S39" s="76"/>
+      <c r="B39" s="33"/>
+      <c r="C39" s="44"/>
+      <c r="D39" s="34"/>
+      <c r="E39" s="35"/>
+      <c r="F39" s="36"/>
+      <c r="G39" s="37"/>
+      <c r="H39" s="36"/>
+      <c r="I39" s="37"/>
+      <c r="J39" s="36"/>
+      <c r="K39" s="37"/>
+      <c r="L39" s="37"/>
+      <c r="M39" s="37"/>
+      <c r="N39" s="75" t="s">
+        <v>186</v>
+      </c>
+      <c r="O39" s="76"/>
+      <c r="P39" s="76"/>
+      <c r="Q39" s="65">
+        <f>SUM(Q10:Q38)</f>
+        <v>132.76740000000001</v>
+      </c>
+      <c r="R39" s="71"/>
+      <c r="S39" s="72"/>
+    </row>
+    <row r="40" spans="1:19" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A40" s="1"/>
+      <c r="B40" s="25"/>
+      <c r="C40" s="45"/>
+      <c r="D40" s="9"/>
+      <c r="E40" s="10"/>
+      <c r="F40" s="10"/>
+      <c r="G40" s="10"/>
+      <c r="H40" s="10"/>
+      <c r="I40" s="10"/>
+      <c r="J40" s="10"/>
+      <c r="K40" s="10"/>
+      <c r="L40" s="10"/>
+      <c r="M40" s="10"/>
+      <c r="N40" s="75" t="s">
+        <v>187</v>
+      </c>
+      <c r="O40" s="76"/>
+      <c r="P40" s="76"/>
+      <c r="Q40" s="66">
+        <f>Q39/10</f>
+        <v>13.27674</v>
+      </c>
+      <c r="R40" s="73"/>
+      <c r="S40" s="74"/>
     </row>
   </sheetData>
   <mergeCells count="5">
     <mergeCell ref="K1:S1"/>
     <mergeCell ref="S3:S8"/>
-    <mergeCell ref="R38:S39"/>
-    <mergeCell ref="N38:P38"/>
+    <mergeCell ref="R39:S40"/>
     <mergeCell ref="N39:P39"/>
+    <mergeCell ref="N40:P40"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="O10" r:id="rId1" xr:uid="{F4798567-38A0-43E2-9A57-E54AB1915E85}"/>
@@ -3604,29 +3669,30 @@
     <hyperlink ref="O13" r:id="rId4" xr:uid="{C794FEA1-1280-480D-9C5A-555269C50D70}"/>
     <hyperlink ref="O14" r:id="rId5" xr:uid="{BF40CE75-30A2-4BFD-B0CE-BD87CCBE0AD6}"/>
     <hyperlink ref="O15" r:id="rId6" xr:uid="{85E985E6-A1AE-4684-BAB6-E780D442FF70}"/>
-    <hyperlink ref="O16" r:id="rId7" xr:uid="{DE2A9CDF-49F2-4FCF-8150-901C47C3B299}"/>
-    <hyperlink ref="O17" r:id="rId8" xr:uid="{16530F95-63A1-4D93-B882-BCCBF62F70D5}"/>
-    <hyperlink ref="O19" r:id="rId9" xr:uid="{202C0AC1-3D2F-4107-BAF9-59640297F8D1}"/>
-    <hyperlink ref="O20" r:id="rId10" xr:uid="{CDB8A34B-8B61-4CE8-9DF9-AFB18DC8AFA4}"/>
-    <hyperlink ref="O21" r:id="rId11" xr:uid="{15984F1D-F20E-4036-ACE1-B542B1BA25B5}"/>
-    <hyperlink ref="O22" r:id="rId12" xr:uid="{498583F1-9D9D-4069-BEBF-AE1D26ED26B5}"/>
-    <hyperlink ref="O24" r:id="rId13" xr:uid="{FB49130B-4676-45E7-8789-AB97FA21BE14}"/>
-    <hyperlink ref="O23" r:id="rId14" xr:uid="{68224F4F-B478-4284-9D0F-DDB1B7AC622C}"/>
-    <hyperlink ref="O25" r:id="rId15" xr:uid="{284E98D7-94C2-4FA5-9714-3F8EB889D64D}"/>
-    <hyperlink ref="O28" r:id="rId16" xr:uid="{7ECC6056-B90E-4A1A-AB0E-3E25B5B02524}"/>
-    <hyperlink ref="O27" r:id="rId17" xr:uid="{4420268E-2D08-4545-92A8-F745BF934ABF}"/>
-    <hyperlink ref="O30" r:id="rId18" xr:uid="{DF3A801F-21BF-4D7B-84CA-189C7521114D}"/>
-    <hyperlink ref="O32" r:id="rId19" xr:uid="{721E5E05-EFF5-452A-B7D5-599A25E1068F}"/>
-    <hyperlink ref="O33" r:id="rId20" xr:uid="{B75313CD-7421-4557-B17A-12DA933D9D33}"/>
-    <hyperlink ref="O36" r:id="rId21" xr:uid="{01E3417C-EB7C-49EE-A0C1-F26D70C08CA9}"/>
-    <hyperlink ref="O35" r:id="rId22" xr:uid="{170A10E6-2632-4E80-9290-22C344C8B67F}"/>
-    <hyperlink ref="O18" r:id="rId23" xr:uid="{ACA5EFEC-F85C-48B9-8C67-8CE59A6B862F}"/>
-    <hyperlink ref="O29" r:id="rId24" xr:uid="{091CBD23-D921-4015-985B-E6E20A2DF817}"/>
-    <hyperlink ref="O31" r:id="rId25" xr:uid="{8575D59F-B099-440F-800D-AFD59FD7E1E8}"/>
-    <hyperlink ref="O26" r:id="rId26" xr:uid="{676A6DD4-A39A-4B44-91A9-93161623CA1F}"/>
+    <hyperlink ref="O18" r:id="rId7" xr:uid="{16530F95-63A1-4D93-B882-BCCBF62F70D5}"/>
+    <hyperlink ref="O20" r:id="rId8" xr:uid="{202C0AC1-3D2F-4107-BAF9-59640297F8D1}"/>
+    <hyperlink ref="O21" r:id="rId9" xr:uid="{CDB8A34B-8B61-4CE8-9DF9-AFB18DC8AFA4}"/>
+    <hyperlink ref="O22" r:id="rId10" xr:uid="{15984F1D-F20E-4036-ACE1-B542B1BA25B5}"/>
+    <hyperlink ref="O23" r:id="rId11" xr:uid="{498583F1-9D9D-4069-BEBF-AE1D26ED26B5}"/>
+    <hyperlink ref="O25" r:id="rId12" xr:uid="{FB49130B-4676-45E7-8789-AB97FA21BE14}"/>
+    <hyperlink ref="O24" r:id="rId13" xr:uid="{68224F4F-B478-4284-9D0F-DDB1B7AC622C}"/>
+    <hyperlink ref="O26" r:id="rId14" xr:uid="{284E98D7-94C2-4FA5-9714-3F8EB889D64D}"/>
+    <hyperlink ref="O29" r:id="rId15" xr:uid="{7ECC6056-B90E-4A1A-AB0E-3E25B5B02524}"/>
+    <hyperlink ref="O28" r:id="rId16" xr:uid="{4420268E-2D08-4545-92A8-F745BF934ABF}"/>
+    <hyperlink ref="O31" r:id="rId17" xr:uid="{DF3A801F-21BF-4D7B-84CA-189C7521114D}"/>
+    <hyperlink ref="O33" r:id="rId18" xr:uid="{B75313CD-7421-4557-B17A-12DA933D9D33}"/>
+    <hyperlink ref="O37" r:id="rId19" xr:uid="{01E3417C-EB7C-49EE-A0C1-F26D70C08CA9}"/>
+    <hyperlink ref="O36" r:id="rId20" xr:uid="{170A10E6-2632-4E80-9290-22C344C8B67F}"/>
+    <hyperlink ref="O19" r:id="rId21" xr:uid="{ACA5EFEC-F85C-48B9-8C67-8CE59A6B862F}"/>
+    <hyperlink ref="O30" r:id="rId22" xr:uid="{091CBD23-D921-4015-985B-E6E20A2DF817}"/>
+    <hyperlink ref="O32" r:id="rId23" xr:uid="{8575D59F-B099-440F-800D-AFD59FD7E1E8}"/>
+    <hyperlink ref="O27" r:id="rId24" xr:uid="{676A6DD4-A39A-4B44-91A9-93161623CA1F}"/>
+    <hyperlink ref="O16" r:id="rId25" xr:uid="{2C85A1F3-A45E-4A11-A9F1-835C6AB31CB5}"/>
+    <hyperlink ref="O17" r:id="rId26" xr:uid="{AD651471-4683-41C5-B82A-32847A4B149A}"/>
+    <hyperlink ref="O34" r:id="rId27" xr:uid="{498B5F24-195D-4071-AB9B-04204292BE44}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId27"/>
-  <drawing r:id="rId28"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId28"/>
+  <drawing r:id="rId29"/>
 </worksheet>
 </file>